--- a/LabDesignWorksheet.xlsx
+++ b/LabDesignWorksheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Analyst Amy\Desktop\TCC\TCC Cybersec\COSC1436LABS\Chapter1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Analyst Amy\Desktop\TCC\TCC Cybersec\COSC1436LABS\Chapter2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C45A04-A9B8-4C0D-9033-48FF7AA6C1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106EDA5B-900D-4DCA-9DEE-3BDCCF80B724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>Author:</t>
   </si>
@@ -142,61 +142,49 @@
     <t>Chandra Peters-Chaney</t>
   </si>
   <si>
-    <t>Restaurant Bill</t>
-  </si>
-  <si>
-    <t>Restaurant Bill Program</t>
-  </si>
-  <si>
-    <t>Meal Cost - $88.67</t>
-  </si>
-  <si>
-    <t>Tax Rate - 6.75%</t>
-  </si>
-  <si>
-    <t>Tip Rate - 20%</t>
-  </si>
-  <si>
-    <t>Store meal cost $88.67</t>
-  </si>
-  <si>
-    <t>tax = meal cost * 0.0675</t>
-  </si>
-  <si>
-    <t>subtotal = meal cost + tax</t>
-  </si>
-  <si>
-    <t>tip = subtotal * 0.20</t>
-  </si>
-  <si>
-    <t>total bill = subtotal + tip</t>
-  </si>
-  <si>
-    <t>meal cost                                           $88.67</t>
-  </si>
-  <si>
-    <t>tax = 88.67 * 0.0675 =                     $5.99</t>
-  </si>
-  <si>
-    <t>subtotal = 88.67 + 5.99 =                $94.66</t>
-  </si>
-  <si>
-    <t>tip = 94.66 * 0.20 =                           $18.93</t>
-  </si>
-  <si>
-    <t>total bill = 94.66 + 18.93 =             $113.59</t>
-  </si>
-  <si>
-    <t>extras</t>
+    <t>Paint</t>
+  </si>
+  <si>
+    <t>Paint Amount Program</t>
+  </si>
+  <si>
+    <t>Paint Area = Area * 2</t>
+  </si>
+  <si>
+    <t>Gallons = Paint Area /340</t>
+  </si>
+  <si>
+    <t>EXTRAS</t>
+  </si>
+  <si>
+    <t>Fence Area = Height * Length</t>
+  </si>
+  <si>
+    <t>Fence Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paint Area </t>
+  </si>
+  <si>
+    <t>Gallons Needed</t>
+  </si>
+  <si>
+    <t>Fence Height = 6'</t>
+  </si>
+  <si>
+    <t>Fence Length = 100'</t>
+  </si>
+  <si>
+    <t>Paint Coverage 340 sqft</t>
+  </si>
+  <si>
+    <t>Approximately</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -209,10 +197,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Consolas"/>
+      <family val="3"/>
     </font>
     <font>
       <b/>
@@ -503,50 +493,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -556,19 +548,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -976,92 +966,92 @@
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="12" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="12" t="s">
+      <c r="D4" s="31"/>
+      <c r="E4" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="13"/>
+      <c r="F4" s="31"/>
     </row>
     <row r="5" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="14" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="42"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="16" t="s">
+      <c r="A6" s="21"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="22"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="16" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="16" t="s">
+      <c r="D7" s="22"/>
+      <c r="E7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="17"/>
+      <c r="F7" s="22"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="17"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="22"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="17"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="22"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="22"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="17"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="22"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="26"/>
     </row>
     <row r="13" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
@@ -1088,266 +1078,266 @@
       <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="21"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="21"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="21"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="21"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="21"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="21"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="21"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
+      <c r="A31" s="23"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="21"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
+      <c r="A33" s="23"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="21"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="21"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="21"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="21"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="21"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="21"/>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="21"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
+      <c r="A41" s="23"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="21"/>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
+      <c r="A42" s="23"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="21"/>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
+      <c r="A43" s="23"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="21"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
+      <c r="A44" s="23"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="21"/>
-      <c r="B45" s="21"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
+      <c r="A45" s="23"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="21"/>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
+      <c r="A46" s="23"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="21"/>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
+      <c r="A47" s="23"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="21"/>
-      <c r="B48" s="21"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
+      <c r="A48" s="23"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="23"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="21"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
+      <c r="A49" s="23"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="21"/>
-      <c r="B50" s="21"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
+      <c r="A50" s="23"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="21"/>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
+      <c r="A51" s="23"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="21"/>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
+      <c r="A52" s="23"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
+      <c r="A53" s="23"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="23"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
+      <c r="A54" s="23"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="21"/>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
+      <c r="A55" s="23"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
+      <c r="A56" s="23"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
     </row>
     <row r="57" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="21"/>
-      <c r="B57" s="21"/>
-      <c r="C57" s="21"/>
-      <c r="D57" s="21"/>
+      <c r="A57" s="23"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="21"/>
-      <c r="B58" s="21"/>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
+      <c r="A58" s="23"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="21"/>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
+      <c r="A59" s="23"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="23"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
@@ -1355,109 +1345,124 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="22"/>
-      <c r="B62" s="21"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
+      <c r="A62" s="39"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="23"/>
+      <c r="D62" s="23"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="21"/>
-      <c r="B63" s="21"/>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
+      <c r="A63" s="23"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="21"/>
-      <c r="B64" s="21"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="23"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="21"/>
-      <c r="B65" s="21"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
+      <c r="A65" s="23"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="23"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="21"/>
-      <c r="B66" s="21"/>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
+      <c r="A66" s="23"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="23"/>
+      <c r="D66" s="23"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="21"/>
-      <c r="B67" s="21"/>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
+      <c r="A67" s="23"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="23"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="21"/>
-      <c r="B68" s="21"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
+      <c r="A68" s="23"/>
+      <c r="B68" s="23"/>
+      <c r="C68" s="23"/>
+      <c r="D68" s="23"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="21"/>
-      <c r="B69" s="21"/>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
+      <c r="A69" s="23"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="23"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="21"/>
-      <c r="B70" s="21"/>
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
+      <c r="A70" s="23"/>
+      <c r="B70" s="23"/>
+      <c r="C70" s="23"/>
+      <c r="D70" s="23"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="21"/>
-      <c r="B71" s="21"/>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
+      <c r="A71" s="23"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="23"/>
+      <c r="D71" s="23"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="21"/>
-      <c r="B72" s="21"/>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
+      <c r="A72" s="23"/>
+      <c r="B72" s="23"/>
+      <c r="C72" s="23"/>
+      <c r="D72" s="23"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="21"/>
-      <c r="B73" s="21"/>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
+      <c r="A73" s="23"/>
+      <c r="B73" s="23"/>
+      <c r="C73" s="23"/>
+      <c r="D73" s="23"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="21"/>
-      <c r="B74" s="21"/>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
+      <c r="A74" s="23"/>
+      <c r="B74" s="23"/>
+      <c r="C74" s="23"/>
+      <c r="D74" s="23"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="21"/>
-      <c r="B75" s="21"/>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
+      <c r="A75" s="23"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="23"/>
+      <c r="D75" s="23"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="21"/>
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
+      <c r="A76" s="23"/>
+      <c r="B76" s="23"/>
+      <c r="C76" s="23"/>
+      <c r="D76" s="23"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="21"/>
-      <c r="B77" s="21"/>
-      <c r="C77" s="21"/>
-      <c r="D77" s="21"/>
+      <c r="A77" s="23"/>
+      <c r="B77" s="23"/>
+      <c r="C77" s="23"/>
+      <c r="D77" s="23"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="21"/>
-      <c r="B78" s="21"/>
-      <c r="C78" s="21"/>
-      <c r="D78" s="21"/>
+      <c r="A78" s="23"/>
+      <c r="B78" s="23"/>
+      <c r="C78" s="23"/>
+      <c r="D78" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="A62:D78"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:D8"/>
@@ -1473,21 +1478,6 @@
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="A18:D59"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -1505,6 +1495,7 @@
     <col min="4" max="4" width="49.7109375" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" customWidth="1"/>
     <col min="6" max="6" width="28.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1520,13 +1511,13 @@
       <c r="D1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="39">
+      <c r="F1" s="19">
         <v>46178</v>
       </c>
-      <c r="G1" s="40"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -1541,29 +1532,28 @@
       <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="40"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="30"/>
+      <c r="E3" s="15"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="12" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="24"/>
+      <c r="D4" s="32"/>
       <c r="E4" s="36" t="s">
         <v>8</v>
       </c>
@@ -1571,180 +1561,207 @@
       <c r="G4" s="38"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="34"/>
+      <c r="C5" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="35"/>
+      <c r="E5" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="23"/>
+      <c r="G5" s="44">
+        <f>G16*G17</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="21"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="44"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="41">
-        <v>88.67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="30"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="D7" s="23"/>
+      <c r="E7" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="23"/>
+      <c r="G7" s="44">
+        <f>G5*G18</f>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="21"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="44"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="41">
-        <f>G5*G16</f>
-        <v>5.9852250000000007</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="32" t="s">
+      <c r="D9" s="23"/>
+      <c r="E9" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="23"/>
+      <c r="G9" s="44">
+        <f>G7/G15</f>
+        <v>3.5294117647058822</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="44"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="41">
-        <f>G5+G7</f>
-        <v>94.655225000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="F11" s="23"/>
+      <c r="G11" s="45">
+        <f>G9</f>
+        <v>3.5294117647058822</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="44"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="21"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="44"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="21"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="26"/>
-      <c r="G9" s="41">
-        <f>G8*G17</f>
-        <v>18.931045000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="26"/>
-      <c r="G10" s="41">
-        <f>G8+G9</f>
-        <v>113.58627</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="30"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="30"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="30"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="30"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="43" t="s">
-        <v>40</v>
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="16">
+        <v>340</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="44">
-        <v>6.7500000000000004E-2</v>
+      <c r="A16" s="21"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="17">
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="44">
-        <v>0.2</v>
+      <c r="A17" s="21"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="17">
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="18"/>
+      <c r="A18" s="25"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="27"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="45"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="18">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="A17:B17"/>
@@ -1761,37 +1778,6 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
